--- a/docs/downloads/05/tbl_water_alaotra_tous.xlsx
+++ b/docs/downloads/05/tbl_water_alaotra_tous.xlsx
@@ -405,12 +405,6 @@
           <t>Cours d?eau</t>
         </is>
       </c>
-      <c r="C3">
-        <v>1</v>
-      </c>
-      <c r="D3">
-        <v>3.2</v>
-      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -423,12 +417,6 @@
           <t>Puits non aménagé (trou d?eau)</t>
         </is>
       </c>
-      <c r="C4">
-        <v>2</v>
-      </c>
-      <c r="D4">
-        <v>6.5</v>
-      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -459,12 +447,6 @@
           <t>Cours d?eau</t>
         </is>
       </c>
-      <c r="C6">
-        <v>4</v>
-      </c>
-      <c r="D6">
-        <v>5.9</v>
-      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -513,12 +495,6 @@
           <t>Source</t>
         </is>
       </c>
-      <c r="C9">
-        <v>2</v>
-      </c>
-      <c r="D9">
-        <v>2.9</v>
-      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -531,12 +507,6 @@
           <t>Autre ____________________________</t>
         </is>
       </c>
-      <c r="C10">
-        <v>4</v>
-      </c>
-      <c r="D10">
-        <v>6.9</v>
-      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -621,12 +591,6 @@
           <t>Autre ____________________________</t>
         </is>
       </c>
-      <c r="C15">
-        <v>3</v>
-      </c>
-      <c r="D15">
-        <v>6.5</v>
-      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -657,12 +621,6 @@
           <t>Cours d?eau</t>
         </is>
       </c>
-      <c r="C17">
-        <v>1</v>
-      </c>
-      <c r="D17">
-        <v>2.2</v>
-      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -675,12 +633,6 @@
           <t>Eau courante dans la maison/dans la cour</t>
         </is>
       </c>
-      <c r="C18">
-        <v>1</v>
-      </c>
-      <c r="D18">
-        <v>2.2</v>
-      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -711,12 +663,6 @@
           <t>Source</t>
         </is>
       </c>
-      <c r="C20">
-        <v>2</v>
-      </c>
-      <c r="D20">
-        <v>4.3</v>
-      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -747,12 +693,6 @@
           <t>Cours d?eau</t>
         </is>
       </c>
-      <c r="C22">
-        <v>1</v>
-      </c>
-      <c r="D22">
-        <v>1.1</v>
-      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -760,12 +700,6 @@
           <t>Alaotra - Avaradrano</t>
         </is>
       </c>
-      <c r="C23">
-        <v>1</v>
-      </c>
-      <c r="D23">
-        <v>1.1</v>
-      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -796,12 +730,6 @@
           <t>Eau courante dans la maison/dans la cour</t>
         </is>
       </c>
-      <c r="C25">
-        <v>1</v>
-      </c>
-      <c r="D25">
-        <v>1.1</v>
-      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -814,12 +742,6 @@
           <t>Puits (margelle)</t>
         </is>
       </c>
-      <c r="C26">
-        <v>3</v>
-      </c>
-      <c r="D26">
-        <v>3.4</v>
-      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -886,12 +808,6 @@
           <t>Eau courante dans la maison/dans la cour</t>
         </is>
       </c>
-      <c r="C30">
-        <v>1</v>
-      </c>
-      <c r="D30">
-        <v>1.4</v>
-      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1024,12 +940,6 @@
         <is>
           <t>Alaotra - Tous</t>
         </is>
-      </c>
-      <c r="C38">
-        <v>1</v>
-      </c>
-      <c r="D38">
-        <v>0.2</v>
       </c>
     </row>
   </sheetData>

--- a/docs/downloads/05/tbl_water_alaotra_tous.xlsx
+++ b/docs/downloads/05/tbl_water_alaotra_tous.xlsx
@@ -379,7 +379,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Alaotra - Ambatoharanana</t>
+          <t>Ambatoharanana</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -397,7 +397,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Alaotra - Ambatoharanana</t>
+          <t>Ambatoharanana</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -409,7 +409,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Alaotra - Ambatoharanana</t>
+          <t>Ambatoharanana</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -421,7 +421,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Alaotra - Ambatoharanana</t>
+          <t>Ambatoharanana</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -439,7 +439,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Alaotra - Ambatomanga</t>
+          <t>Ambatomanga</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -451,7 +451,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Alaotra - Ambatomanga</t>
+          <t>Ambatomanga</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -469,7 +469,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Alaotra - Ambatomanga</t>
+          <t>Ambatomanga</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -487,7 +487,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Alaotra - Ambatomanga</t>
+          <t>Ambatomanga</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -499,7 +499,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Alaotra - Ambodivoara</t>
+          <t>Ambodivoara</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -511,7 +511,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Alaotra - Ambodivoara</t>
+          <t>Ambodivoara</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -529,7 +529,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Alaotra - Ambodivoara</t>
+          <t>Ambodivoara</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -547,7 +547,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Alaotra - Ambohidrony</t>
+          <t>Ambohidrony</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -565,7 +565,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Alaotra - Ambohidrony</t>
+          <t>Ambohidrony</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -583,7 +583,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Alaotra - Analamiranga</t>
+          <t>Analamiranga</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -595,7 +595,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Alaotra - Analamiranga</t>
+          <t>Analamiranga</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -613,7 +613,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Alaotra - Analamiranga</t>
+          <t>Analamiranga</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -625,7 +625,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Alaotra - Analamiranga</t>
+          <t>Analamiranga</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -637,7 +637,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Alaotra - Analamiranga</t>
+          <t>Analamiranga</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -655,7 +655,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Alaotra - Analamiranga</t>
+          <t>Analamiranga</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -667,7 +667,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Alaotra - Avaradrano</t>
+          <t>Avaradrano</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -685,7 +685,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Alaotra - Avaradrano</t>
+          <t>Avaradrano</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -697,14 +697,14 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Alaotra - Avaradrano</t>
+          <t>Avaradrano</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Alaotra - Feramanga Atsimo</t>
+          <t>Feramanga Atsimo</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -722,7 +722,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Alaotra - Feramanga Atsimo</t>
+          <t>Feramanga Atsimo</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -734,7 +734,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Alaotra - Feramanga Atsimo</t>
+          <t>Feramanga Atsimo</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -746,7 +746,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Alaotra - Feramanga Atsimo</t>
+          <t>Feramanga Atsimo</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -764,7 +764,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Alaotra - Feramanga Atsimo</t>
+          <t>Feramanga Atsimo</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -782,7 +782,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Alaotra - Mangabe</t>
+          <t>Mangabe</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -800,7 +800,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Alaotra - Mangabe</t>
+          <t>Mangabe</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -812,7 +812,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Alaotra - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -830,7 +830,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Alaotra - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -848,7 +848,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Alaotra - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -866,7 +866,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Alaotra - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -884,7 +884,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Alaotra - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -902,7 +902,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Alaotra - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -920,7 +920,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Alaotra - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -938,7 +938,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Alaotra - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
     </row>
